--- a/static/战绩.xlsx
+++ b/static/战绩.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="10640" windowHeight="12080"/>
+    <workbookView windowWidth="12220" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2427" uniqueCount="483">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2448" uniqueCount="485">
   <si>
     <t>时间</t>
   </si>
@@ -1476,6 +1476,12 @@
   </si>
   <si>
     <t>KSG vs WST</t>
+  </si>
+  <si>
+    <t>2026.07.10</t>
+  </si>
+  <si>
+    <t>2/2/6</t>
   </si>
 </sst>
 </file>
@@ -3331,7 +3337,6 @@
       <c r="D27" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="E27"/>
       <c r="F27" t="s">
         <v>32</v>
       </c>
@@ -12885,7 +12890,7 @@
         <v>2</v>
       </c>
       <c r="F467" t="s">
-        <v>275</v>
+        <v>25</v>
       </c>
       <c r="G467" s="3" t="s">
         <v>433</v>
@@ -14789,25 +14794,112 @@
         <v>24</v>
       </c>
     </row>
-    <row r="556" spans="4:7">
-      <c r="D556" s="3"/>
-      <c r="G556" s="3"/>
-    </row>
-    <row r="557" spans="4:7">
+    <row r="556" spans="1:12">
+      <c r="A556" t="s">
+        <v>483</v>
+      </c>
+      <c r="B556" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="C556" t="s">
+        <v>436</v>
+      </c>
+      <c r="D556" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E556">
+        <v>1</v>
+      </c>
+      <c r="F556" t="s">
+        <v>58</v>
+      </c>
+      <c r="G556" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="H556" s="1">
+        <v>0.0151157407407407</v>
+      </c>
+      <c r="I556" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L556" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="557" spans="4:9">
       <c r="D557" s="3"/>
-      <c r="G557" s="3"/>
-    </row>
-    <row r="558" spans="4:7">
+      <c r="E557">
+        <v>2</v>
+      </c>
+      <c r="F557" t="s">
+        <v>364</v>
+      </c>
+      <c r="G557" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="H557" s="1">
+        <v>0.00832175925925926</v>
+      </c>
+      <c r="I557" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="558" spans="4:10">
       <c r="D558" s="3"/>
-      <c r="G558" s="3"/>
-    </row>
-    <row r="559" spans="4:7">
+      <c r="E558">
+        <v>3</v>
+      </c>
+      <c r="F558" t="s">
+        <v>400</v>
+      </c>
+      <c r="G558" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="H558" s="1">
+        <v>0.0111226851851852</v>
+      </c>
+      <c r="I558" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="J558" s="8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="559" spans="4:9">
       <c r="D559" s="3"/>
-      <c r="G559" s="3"/>
-    </row>
-    <row r="560" spans="4:7">
+      <c r="E559">
+        <v>4</v>
+      </c>
+      <c r="F559" t="s">
+        <v>32</v>
+      </c>
+      <c r="G559" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H559" s="1">
+        <v>0.00943287037037037</v>
+      </c>
+      <c r="I559" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="560" spans="4:9">
       <c r="D560" s="3"/>
-      <c r="G560" s="3"/>
+      <c r="E560">
+        <v>5</v>
+      </c>
+      <c r="F560" t="s">
+        <v>52</v>
+      </c>
+      <c r="G560" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H560" s="1">
+        <v>0.0104861111111111</v>
+      </c>
+      <c r="I560" s="6" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="561" spans="4:7">
       <c r="D561" s="3"/>

--- a/static/战绩.xlsx
+++ b/static/战绩.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="12220" windowHeight="12080"/>
+    <workbookView windowWidth="11950" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2448" uniqueCount="485">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2462" uniqueCount="487">
   <si>
     <t>时间</t>
   </si>
@@ -1482,6 +1482,12 @@
   </si>
   <si>
     <t>2/2/6</t>
+  </si>
+  <si>
+    <t>2026.07.12</t>
+  </si>
+  <si>
+    <t>4/2/1</t>
   </si>
 </sst>
 </file>
@@ -14901,17 +14907,73 @@
         <v>18</v>
       </c>
     </row>
-    <row r="561" spans="4:7">
-      <c r="D561" s="3"/>
-      <c r="G561" s="3"/>
-    </row>
-    <row r="562" spans="4:7">
+    <row r="561" spans="1:12">
+      <c r="A561" t="s">
+        <v>485</v>
+      </c>
+      <c r="B561" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="C561" t="s">
+        <v>421</v>
+      </c>
+      <c r="D561" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="E561">
+        <v>1</v>
+      </c>
+      <c r="F561" t="s">
+        <v>52</v>
+      </c>
+      <c r="G561" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="H561" s="1">
+        <v>0.0116435185185185</v>
+      </c>
+      <c r="I561" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L561" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="562" spans="4:9">
       <c r="D562" s="3"/>
-      <c r="G562" s="3"/>
-    </row>
-    <row r="563" spans="4:7">
+      <c r="E562">
+        <v>2</v>
+      </c>
+      <c r="F562" t="s">
+        <v>400</v>
+      </c>
+      <c r="G562" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="H562" s="1">
+        <v>0.0133333333333333</v>
+      </c>
+      <c r="I562" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="563" spans="4:9">
       <c r="D563" s="3"/>
-      <c r="G563" s="3"/>
+      <c r="E563">
+        <v>3</v>
+      </c>
+      <c r="F563" t="s">
+        <v>25</v>
+      </c>
+      <c r="G563" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="H563" s="1">
+        <v>0.0161458333333333</v>
+      </c>
+      <c r="I563" s="6" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="564" spans="4:7">
       <c r="D564" s="3"/>

--- a/static/战绩.xlsx
+++ b/static/战绩.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2462" uniqueCount="487">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2482" uniqueCount="491">
   <si>
     <t>时间</t>
   </si>
@@ -1488,6 +1488,18 @@
   </si>
   <si>
     <t>4/2/1</t>
+  </si>
+  <si>
+    <t>2026.07.17</t>
+  </si>
+  <si>
+    <t>无言、句号、小屿、烈峰峰</t>
+  </si>
+  <si>
+    <t>0/0/9</t>
+  </si>
+  <si>
+    <t>1/6/2</t>
   </si>
 </sst>
 </file>
@@ -14975,25 +14987,109 @@
         <v>18</v>
       </c>
     </row>
-    <row r="564" spans="4:7">
-      <c r="D564" s="3"/>
-      <c r="G564" s="3"/>
-    </row>
-    <row r="565" spans="4:7">
+    <row r="564" spans="1:12">
+      <c r="A564" t="s">
+        <v>487</v>
+      </c>
+      <c r="B564" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="C564" t="s">
+        <v>413</v>
+      </c>
+      <c r="D564" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E564">
+        <v>1</v>
+      </c>
+      <c r="F564" t="s">
+        <v>308</v>
+      </c>
+      <c r="G564" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H564" s="1">
+        <v>0.0154976851851852</v>
+      </c>
+      <c r="I564" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L564" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="565" spans="4:9">
       <c r="D565" s="3"/>
-      <c r="G565" s="3"/>
-    </row>
-    <row r="566" spans="4:7">
+      <c r="E565">
+        <v>2</v>
+      </c>
+      <c r="F565" t="s">
+        <v>400</v>
+      </c>
+      <c r="G565" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="H565" s="1">
+        <v>0.00957175925925926</v>
+      </c>
+      <c r="I565" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="566" spans="4:9">
       <c r="D566" s="3"/>
-      <c r="G566" s="3"/>
-    </row>
-    <row r="567" spans="4:7">
+      <c r="E566">
+        <v>3</v>
+      </c>
+      <c r="F566" t="s">
+        <v>52</v>
+      </c>
+      <c r="G566" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="H566" s="1">
+        <v>0.00850694444444444</v>
+      </c>
+      <c r="I566" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="567" spans="4:9">
       <c r="D567" s="3"/>
-      <c r="G567" s="3"/>
-    </row>
-    <row r="568" spans="4:7">
+      <c r="E567">
+        <v>4</v>
+      </c>
+      <c r="F567" t="s">
+        <v>27</v>
+      </c>
+      <c r="G567" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="H567" s="1">
+        <v>0.0126157407407407</v>
+      </c>
+      <c r="I567" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="568" spans="4:9">
       <c r="D568" s="3"/>
-      <c r="G568" s="3"/>
+      <c r="E568">
+        <v>5</v>
+      </c>
+      <c r="F568" t="s">
+        <v>45</v>
+      </c>
+      <c r="G568" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="H568" s="1">
+        <v>0.0145601851851852</v>
+      </c>
+      <c r="I568" s="6" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="569" spans="4:7">
       <c r="D569" s="3"/>

--- a/static/战绩.xlsx
+++ b/static/战绩.xlsx
@@ -13225,7 +13225,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="482" spans="1:9">
+    <row r="482" spans="1:12">
       <c r="A482" t="s">
         <v>442</v>
       </c>
@@ -13253,8 +13253,11 @@
       <c r="I482" s="7" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="483" spans="4:12">
+      <c r="L482" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="483" spans="4:9">
       <c r="D483" s="3"/>
       <c r="E483">
         <v>2</v>
@@ -13270,9 +13273,6 @@
       </c>
       <c r="I483" s="7" t="s">
         <v>24</v>
-      </c>
-      <c r="L483" t="s">
-        <v>419</v>
       </c>
     </row>
     <row r="484" spans="4:9">

--- a/static/战绩.xlsx
+++ b/static/战绩.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2482" uniqueCount="491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2513" uniqueCount="494">
   <si>
     <t>时间</t>
   </si>
@@ -1500,6 +1500,15 @@
   </si>
   <si>
     <t>1/6/2</t>
+  </si>
+  <si>
+    <t>2026.07.22</t>
+  </si>
+  <si>
+    <t>KSG vs 杭州LGD.NBW</t>
+  </si>
+  <si>
+    <t>2026.07.25</t>
   </si>
 </sst>
 </file>
@@ -15091,36 +15100,163 @@
         <v>18</v>
       </c>
     </row>
-    <row r="569" spans="4:7">
-      <c r="D569" s="3"/>
-      <c r="G569" s="3"/>
-    </row>
-    <row r="570" spans="4:7">
+    <row r="569" spans="1:12">
+      <c r="A569" t="s">
+        <v>491</v>
+      </c>
+      <c r="B569" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="C569" t="s">
+        <v>492</v>
+      </c>
+      <c r="D569" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E569">
+        <v>1</v>
+      </c>
+      <c r="F569" t="s">
+        <v>117</v>
+      </c>
+      <c r="G569" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="H569" s="1">
+        <v>0.0146990740740741</v>
+      </c>
+      <c r="I569" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L569" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="570" spans="4:9">
       <c r="D570" s="3"/>
-      <c r="G570" s="3"/>
-    </row>
-    <row r="571" spans="4:7">
+      <c r="E570">
+        <v>2</v>
+      </c>
+      <c r="F570" t="s">
+        <v>400</v>
+      </c>
+      <c r="G570" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="H570" s="1">
+        <v>0.0080787037037037</v>
+      </c>
+      <c r="I570" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="571" spans="4:9">
       <c r="D571" s="3"/>
-      <c r="G571" s="3"/>
-    </row>
-    <row r="572" spans="4:7">
+      <c r="E571">
+        <v>3</v>
+      </c>
+      <c r="F571" t="s">
+        <v>364</v>
+      </c>
+      <c r="G571" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="H571" s="1">
+        <v>0.0091087962962963</v>
+      </c>
+      <c r="I571" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="572" spans="4:9">
       <c r="D572" s="3"/>
-      <c r="G572" s="3"/>
-    </row>
-    <row r="573" spans="4:7">
-      <c r="D573" s="3"/>
-      <c r="G573" s="3"/>
-    </row>
-    <row r="574" spans="4:7">
+      <c r="E572">
+        <v>4</v>
+      </c>
+      <c r="F572" t="s">
+        <v>85</v>
+      </c>
+      <c r="G572" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="H572" s="1">
+        <v>0.0115277777777778</v>
+      </c>
+      <c r="I572" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="573" spans="1:12">
+      <c r="A573" t="s">
+        <v>493</v>
+      </c>
+      <c r="B573" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="C573" t="s">
+        <v>427</v>
+      </c>
+      <c r="D573" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="E573">
+        <v>1</v>
+      </c>
+      <c r="F573" t="s">
+        <v>364</v>
+      </c>
+      <c r="G573" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="H573" s="1">
+        <v>0.0151736111111111</v>
+      </c>
+      <c r="I573" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L573" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="574" spans="4:9">
       <c r="D574" s="3"/>
-      <c r="G574" s="3"/>
-    </row>
-    <row r="575" spans="4:7">
+      <c r="E574">
+        <v>2</v>
+      </c>
+      <c r="F574" t="s">
+        <v>52</v>
+      </c>
+      <c r="G574" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H574" s="1">
+        <v>0.0103240740740741</v>
+      </c>
+      <c r="I574" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="575" spans="4:9">
       <c r="D575" s="3"/>
-      <c r="G575" s="3"/>
+      <c r="E575">
+        <v>3</v>
+      </c>
+      <c r="F575" t="s">
+        <v>341</v>
+      </c>
+      <c r="G575" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H575" s="1">
+        <v>0.00864583333333333</v>
+      </c>
+      <c r="I575" s="6" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="576" spans="4:7">
       <c r="D576" s="3"/>
+      <c r="E576"/>
       <c r="G576" s="3"/>
     </row>
     <row r="577" spans="4:7">

--- a/static/战绩.xlsx
+++ b/static/战绩.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="11950" windowHeight="12080"/>
+    <workbookView windowWidth="11690" windowHeight="11630"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2513" uniqueCount="494">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2564" uniqueCount="504">
   <si>
     <t>时间</t>
   </si>
@@ -1509,6 +1509,36 @@
   </si>
   <si>
     <t>2026.07.25</t>
+  </si>
+  <si>
+    <t>2026.07.28</t>
+  </si>
+  <si>
+    <t>0/0/12</t>
+  </si>
+  <si>
+    <t>2026.07.30</t>
+  </si>
+  <si>
+    <t>KSG vs 上海EDG.M</t>
+  </si>
+  <si>
+    <t>7/2/2</t>
+  </si>
+  <si>
+    <t>2026.08.02</t>
+  </si>
+  <si>
+    <t>2026王者荣耀电竞世俱杯</t>
+  </si>
+  <si>
+    <t>KSG vs RNTX</t>
+  </si>
+  <si>
+    <t>5/0/7</t>
+  </si>
+  <si>
+    <t>洛里昂</t>
   </si>
 </sst>
 </file>
@@ -2173,7 +2203,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2202,6 +2232,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -15254,54 +15287,266 @@
         <v>18</v>
       </c>
     </row>
-    <row r="576" spans="4:7">
-      <c r="D576" s="3"/>
-      <c r="E576"/>
-      <c r="G576" s="3"/>
-    </row>
-    <row r="577" spans="4:7">
+    <row r="576" spans="1:12">
+      <c r="A576" t="s">
+        <v>494</v>
+      </c>
+      <c r="B576" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="C576" t="s">
+        <v>405</v>
+      </c>
+      <c r="D576" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="E576">
+        <v>1</v>
+      </c>
+      <c r="F576" t="s">
+        <v>16</v>
+      </c>
+      <c r="G576" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="H576" s="1">
+        <v>0.0103819444444444</v>
+      </c>
+      <c r="I576" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L576" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="577" spans="4:9">
       <c r="D577" s="3"/>
-      <c r="G577" s="3"/>
-    </row>
-    <row r="578" spans="4:7">
+      <c r="E577">
+        <v>2</v>
+      </c>
+      <c r="F577" t="s">
+        <v>400</v>
+      </c>
+      <c r="G577" s="10">
+        <v>37051</v>
+      </c>
+      <c r="H577" s="1">
+        <v>0.0161689814814815</v>
+      </c>
+      <c r="I577" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="578" spans="4:9">
       <c r="D578" s="3"/>
-      <c r="G578" s="3"/>
-    </row>
-    <row r="579" spans="4:7">
+      <c r="E578">
+        <v>3</v>
+      </c>
+      <c r="F578" t="s">
+        <v>364</v>
+      </c>
+      <c r="G578" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="H578" s="1">
+        <v>0.00916666666666667</v>
+      </c>
+      <c r="I578" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="579" spans="4:9">
       <c r="D579" s="3"/>
-      <c r="G579" s="3"/>
-    </row>
-    <row r="580" spans="4:7">
+      <c r="E579">
+        <v>4</v>
+      </c>
+      <c r="F579" t="s">
+        <v>32</v>
+      </c>
+      <c r="G579" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="H579" s="1">
+        <v>0.0123958333333333</v>
+      </c>
+      <c r="I579" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="580" spans="4:9">
       <c r="D580" s="3"/>
-      <c r="G580" s="3"/>
-    </row>
-    <row r="581" spans="4:7">
-      <c r="D581" s="3"/>
-      <c r="G581" s="3"/>
-    </row>
-    <row r="582" spans="4:7">
+      <c r="E580">
+        <v>5</v>
+      </c>
+      <c r="F580" t="s">
+        <v>25</v>
+      </c>
+      <c r="G580" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="H580" s="1">
+        <v>0.00930555555555555</v>
+      </c>
+      <c r="I580" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="581" spans="1:12">
+      <c r="A581" t="s">
+        <v>496</v>
+      </c>
+      <c r="B581" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="C581" t="s">
+        <v>497</v>
+      </c>
+      <c r="D581" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E581">
+        <v>1</v>
+      </c>
+      <c r="F581" t="s">
+        <v>25</v>
+      </c>
+      <c r="G581" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="H581" s="1">
+        <v>0.0102777777777778</v>
+      </c>
+      <c r="I581" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="J581" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="L581" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="582" spans="4:9">
       <c r="D582" s="3"/>
-      <c r="G582" s="3"/>
-    </row>
-    <row r="583" spans="4:7">
+      <c r="E582">
+        <v>2</v>
+      </c>
+      <c r="F582" t="s">
+        <v>400</v>
+      </c>
+      <c r="G582" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="H582" s="1">
+        <v>0.00969907407407407</v>
+      </c>
+      <c r="I582" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="583" spans="4:9">
       <c r="D583" s="3"/>
-      <c r="G583" s="3"/>
-    </row>
-    <row r="584" spans="4:7">
+      <c r="E583">
+        <v>3</v>
+      </c>
+      <c r="F583" t="s">
+        <v>22</v>
+      </c>
+      <c r="G583" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="H583" s="1">
+        <v>0.0141087962962963</v>
+      </c>
+      <c r="I583" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="584" spans="4:9">
       <c r="D584" s="3"/>
-      <c r="G584" s="3"/>
-    </row>
-    <row r="585" spans="4:7">
+      <c r="E584">
+        <v>4</v>
+      </c>
+      <c r="F584" t="s">
+        <v>27</v>
+      </c>
+      <c r="G584" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="H584" s="1">
+        <v>0.0116319444444444</v>
+      </c>
+      <c r="I584" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="585" spans="4:9">
       <c r="D585" s="3"/>
-      <c r="G585" s="3"/>
-    </row>
-    <row r="586" spans="4:7">
-      <c r="D586" s="3"/>
-      <c r="G586" s="3"/>
-    </row>
-    <row r="587" spans="4:7">
+      <c r="E585">
+        <v>5</v>
+      </c>
+      <c r="F585" t="s">
+        <v>52</v>
+      </c>
+      <c r="G585" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="H585" s="1">
+        <v>0.0121759259259259</v>
+      </c>
+      <c r="I585" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="586" spans="1:12">
+      <c r="A586" t="s">
+        <v>499</v>
+      </c>
+      <c r="B586" t="s">
+        <v>500</v>
+      </c>
+      <c r="C586" t="s">
+        <v>501</v>
+      </c>
+      <c r="D586" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E586">
+        <v>1</v>
+      </c>
+      <c r="F586" t="s">
+        <v>25</v>
+      </c>
+      <c r="G586" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="H586" s="1">
+        <v>0.00672453703703704</v>
+      </c>
+      <c r="I586" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L586" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="587" spans="4:9">
       <c r="D587" s="3"/>
-      <c r="G587" s="3"/>
+      <c r="E587">
+        <v>2</v>
+      </c>
+      <c r="F587" t="s">
+        <v>503</v>
+      </c>
+      <c r="G587" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="H587" s="1">
+        <v>0.0047337962962963</v>
+      </c>
+      <c r="I587" s="7" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="588" spans="4:7">
       <c r="D588" s="3"/>

--- a/static/战绩.xlsx
+++ b/static/战绩.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="11690" windowHeight="11630"/>
+    <workbookView windowWidth="24750" windowHeight="11630"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2564" uniqueCount="504">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2637" uniqueCount="518">
   <si>
     <t>时间</t>
   </si>
@@ -1517,6 +1517,9 @@
     <t>0/0/12</t>
   </si>
   <si>
+    <t>1/6/9</t>
+  </si>
+  <si>
     <t>2026.07.30</t>
   </si>
   <si>
@@ -1539,6 +1542,45 @@
   </si>
   <si>
     <t>洛里昂</t>
+  </si>
+  <si>
+    <t>KSG vs VP</t>
+  </si>
+  <si>
+    <t>2/2/10</t>
+  </si>
+  <si>
+    <t>2026.08.06</t>
+  </si>
+  <si>
+    <t>迦楼罗（嬴政）</t>
+  </si>
+  <si>
+    <t>2026.08.07</t>
+  </si>
+  <si>
+    <t>KSG vs GK</t>
+  </si>
+  <si>
+    <t>2/4/9</t>
+  </si>
+  <si>
+    <t>2026.08.08</t>
+  </si>
+  <si>
+    <t>KSG vs AG.AL</t>
+  </si>
+  <si>
+    <t>0/1/7</t>
+  </si>
+  <si>
+    <t>5/1/2</t>
+  </si>
+  <si>
+    <t>2/2/2</t>
+  </si>
+  <si>
+    <t>4/2/6</t>
   </si>
 </sst>
 </file>
@@ -2203,7 +2245,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2232,9 +2274,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2775,7 +2814,7 @@
     <col min="3" max="3" width="25.2363636363636" customWidth="1"/>
     <col min="4" max="4" width="12.8181818181818"/>
     <col min="5" max="6" width="10.7272727272727" customWidth="1"/>
-    <col min="7" max="7" width="9.54545454545454"/>
+    <col min="7" max="7" width="10.6363636363636"/>
     <col min="8" max="8" width="9.54545454545454" style="1"/>
     <col min="12" max="12" width="26.1818181818182" customWidth="1"/>
   </cols>
@@ -15327,8 +15366,8 @@
       <c r="F577" t="s">
         <v>400</v>
       </c>
-      <c r="G577" s="10">
-        <v>37051</v>
+      <c r="G577" s="3" t="s">
+        <v>496</v>
       </c>
       <c r="H577" s="1">
         <v>0.0161689814814815</v>
@@ -15393,13 +15432,13 @@
     </row>
     <row r="581" spans="1:12">
       <c r="A581" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B581" s="2" t="s">
         <v>471</v>
       </c>
       <c r="C581" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D581" s="3" t="s">
         <v>15</v>
@@ -15411,7 +15450,7 @@
         <v>25</v>
       </c>
       <c r="G581" s="3" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H581" s="1">
         <v>0.0102777777777778</v>
@@ -15500,13 +15539,13 @@
     </row>
     <row r="586" spans="1:12">
       <c r="A586" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B586" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C586" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="D586" s="3" t="s">
         <v>43</v>
@@ -15518,7 +15557,7 @@
         <v>25</v>
       </c>
       <c r="G586" s="3" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H586" s="1">
         <v>0.00672453703703704</v>
@@ -15536,7 +15575,7 @@
         <v>2</v>
       </c>
       <c r="F587" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="G587" s="3" t="s">
         <v>375</v>
@@ -15548,61 +15587,374 @@
         <v>24</v>
       </c>
     </row>
-    <row r="588" spans="4:7">
-      <c r="D588" s="3"/>
-      <c r="G588" s="3"/>
-    </row>
-    <row r="589" spans="4:7">
+    <row r="588" spans="1:12">
+      <c r="A588" t="s">
+        <v>500</v>
+      </c>
+      <c r="B588" t="s">
+        <v>501</v>
+      </c>
+      <c r="C588" t="s">
+        <v>505</v>
+      </c>
+      <c r="D588" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E588">
+        <v>1</v>
+      </c>
+      <c r="F588" t="s">
+        <v>504</v>
+      </c>
+      <c r="G588" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="H588" s="1">
+        <v>0.00842592592592593</v>
+      </c>
+      <c r="I588" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L588" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="589" spans="4:9">
       <c r="D589" s="3"/>
-      <c r="G589" s="3"/>
-    </row>
-    <row r="590" spans="4:4">
-      <c r="D590" s="3"/>
-    </row>
-    <row r="591" spans="4:4">
+      <c r="E589">
+        <v>2</v>
+      </c>
+      <c r="F589" t="s">
+        <v>364</v>
+      </c>
+      <c r="G589" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="H589" s="1">
+        <v>0.009375</v>
+      </c>
+      <c r="I589" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="590" spans="1:12">
+      <c r="A590" t="s">
+        <v>507</v>
+      </c>
+      <c r="B590" t="s">
+        <v>501</v>
+      </c>
+      <c r="C590" t="s">
+        <v>505</v>
+      </c>
+      <c r="D590" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="E590">
+        <v>1</v>
+      </c>
+      <c r="F590" t="s">
+        <v>504</v>
+      </c>
+      <c r="G590" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="H590" s="1">
+        <v>0.00872685185185185</v>
+      </c>
+      <c r="I590" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L590" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="591" spans="4:9">
       <c r="D591" s="3"/>
-    </row>
-    <row r="592" spans="4:4">
+      <c r="E591">
+        <v>2</v>
+      </c>
+      <c r="F591" t="s">
+        <v>32</v>
+      </c>
+      <c r="G591" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="H591" s="1">
+        <v>0.00765046296296296</v>
+      </c>
+      <c r="I591" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="592" spans="4:9">
       <c r="D592" s="3"/>
-    </row>
-    <row r="593" spans="4:4">
+      <c r="E592">
+        <v>3</v>
+      </c>
+      <c r="F592" t="s">
+        <v>159</v>
+      </c>
+      <c r="G592" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="H592" s="1">
+        <v>0.00795138888888889</v>
+      </c>
+      <c r="I592" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="593" spans="4:9">
       <c r="D593" s="3"/>
-    </row>
-    <row r="594" spans="4:4">
-      <c r="D594" s="3"/>
-    </row>
-    <row r="595" spans="4:4">
+      <c r="E593">
+        <v>4</v>
+      </c>
+      <c r="F593" t="s">
+        <v>508</v>
+      </c>
+      <c r="G593" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="H593" s="1">
+        <v>0.0090625</v>
+      </c>
+      <c r="I593" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="594" spans="1:12">
+      <c r="A594" t="s">
+        <v>509</v>
+      </c>
+      <c r="B594" t="s">
+        <v>501</v>
+      </c>
+      <c r="C594" t="s">
+        <v>510</v>
+      </c>
+      <c r="D594" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="E594">
+        <v>1</v>
+      </c>
+      <c r="F594" t="s">
+        <v>32</v>
+      </c>
+      <c r="G594" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="H594" s="1">
+        <v>0.00908564814814815</v>
+      </c>
+      <c r="I594" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L594" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="595" spans="4:9">
       <c r="D595" s="3"/>
-    </row>
-    <row r="596" spans="4:4">
+      <c r="E595">
+        <v>2</v>
+      </c>
+      <c r="F595" t="s">
+        <v>364</v>
+      </c>
+      <c r="G595" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="H595" s="1">
+        <v>0.00893518518518518</v>
+      </c>
+      <c r="I595" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="596" spans="4:9">
       <c r="D596" s="3"/>
-    </row>
-    <row r="597" spans="4:4">
+      <c r="E596">
+        <v>3</v>
+      </c>
+      <c r="F596" t="s">
+        <v>508</v>
+      </c>
+      <c r="G596" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="H596" s="1">
+        <v>0.0158912037037037</v>
+      </c>
+      <c r="I596" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="597" spans="4:9">
       <c r="D597" s="3"/>
-    </row>
-    <row r="598" spans="4:4">
-      <c r="D598" s="3"/>
-    </row>
-    <row r="599" spans="4:4">
+      <c r="E597">
+        <v>4</v>
+      </c>
+      <c r="F597" t="s">
+        <v>25</v>
+      </c>
+      <c r="G597" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="H597" s="1">
+        <v>0.0102199074074074</v>
+      </c>
+      <c r="I597" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="598" spans="1:12">
+      <c r="A598" t="s">
+        <v>512</v>
+      </c>
+      <c r="B598" t="s">
+        <v>501</v>
+      </c>
+      <c r="C598" t="s">
+        <v>513</v>
+      </c>
+      <c r="D598" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="E598">
+        <v>1</v>
+      </c>
+      <c r="F598" t="s">
+        <v>508</v>
+      </c>
+      <c r="G598" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="H598" s="1">
+        <v>0.0132523148148148</v>
+      </c>
+      <c r="I598" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L598" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="599" spans="4:9">
       <c r="D599" s="3"/>
-    </row>
-    <row r="600" spans="4:4">
+      <c r="E599">
+        <v>2</v>
+      </c>
+      <c r="F599" t="s">
+        <v>27</v>
+      </c>
+      <c r="G599" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="H599" s="1">
+        <v>0.0157523148148148</v>
+      </c>
+      <c r="I599" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="600" spans="4:9">
       <c r="D600" s="3"/>
-    </row>
-    <row r="601" spans="4:4">
+      <c r="E600">
+        <v>3</v>
+      </c>
+      <c r="F600" t="s">
+        <v>25</v>
+      </c>
+      <c r="G600" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="H600" s="1">
+        <v>0.0093287037037037</v>
+      </c>
+      <c r="I600" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="601" spans="4:9">
       <c r="D601" s="3"/>
-    </row>
-    <row r="602" spans="4:4">
+      <c r="E601">
+        <v>4</v>
+      </c>
+      <c r="F601" t="s">
+        <v>159</v>
+      </c>
+      <c r="G601" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="H601" s="1">
+        <v>0.0108449074074074</v>
+      </c>
+      <c r="I601" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="602" spans="4:9">
       <c r="D602" s="3"/>
-    </row>
-    <row r="603" spans="4:4">
+      <c r="E602">
+        <v>5</v>
+      </c>
+      <c r="F602" t="s">
+        <v>504</v>
+      </c>
+      <c r="G602" s="3" t="s">
+        <v>516</v>
+      </c>
+      <c r="H602" s="1">
+        <v>0.0139236111111111</v>
+      </c>
+      <c r="I602" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="603" spans="4:9">
       <c r="D603" s="3"/>
-    </row>
-    <row r="604" spans="4:4">
+      <c r="E603">
+        <v>6</v>
+      </c>
+      <c r="F603" t="s">
+        <v>275</v>
+      </c>
+      <c r="G603" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="H603" s="1">
+        <v>0.0144560185185185</v>
+      </c>
+      <c r="I603" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="604" spans="4:11">
       <c r="D604" s="3"/>
-    </row>
-    <row r="605" spans="4:4">
+      <c r="E604">
+        <v>7</v>
+      </c>
+      <c r="F604" t="s">
+        <v>25</v>
+      </c>
+      <c r="G604" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="H604" s="1">
+        <v>0.0083912037037037</v>
+      </c>
+      <c r="I604" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K604" s="8" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="605" spans="4:7">
       <c r="D605" s="3"/>
+      <c r="G605" s="3"/>
     </row>
     <row r="606" spans="4:4">
       <c r="D606" s="3"/>
